--- a/vse-loti/339530089/spec-339530089.xlsx
+++ b/vse-loti/339530089/spec-339530089.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +61,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,19 +436,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,17 +504,116 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ТРУБА 820Х10 СТ17Г1СУ ТИП3 К52 ГОСТ20295</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>9.587999999999999</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>тн</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
+        <v>8201017135220295</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>9841220562264354</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>7.863135229249218e+16</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ТРУБЫ 426Х9 09Г2С ГОСТ10704</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>тн</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="3" t="n">
+        <v>426909210704</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>512291052844.8</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>2433382501012.8</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Срок поставки: сентябрь 2026 г.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>2431.2</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>6078</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>2431.2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>7.863378567499926e+16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Источник: Проект договора (типовой) поставки ТРУБ (партии).docx</t>
         </is>

--- a/vse-loti/339530089/spec-339530089.xlsx
+++ b/vse-loti/339530089/spec-339530089.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.####"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -68,8 +68,8 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -447,8 +447,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +477,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -520,18 +508,11 @@
           <t>тн</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="3" t="n">
-        <v>8201017135220295</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>9841220562264354</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>7.863135229249218e+16</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="E2" s="3" t="n">
+        <v>9.587999999999999</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -550,18 +531,11 @@
           <t>тн</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="3" t="n">
-        <v>426909210704</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>512291052844.8</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>2433382501012.8</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="E3" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -569,51 +543,291 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Продукция должна быть маркирована и упакована в упаковку, обеспечивающую сохранность Продукции от порчи, повреждений при транспортировании всеми видами транспорта, перегрузке, хранении, согласно ГОСТ10692-2015. Тара (упаковка) возврату не подлежит.</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Поставка продукции производится автотранспортом Поставщика до склада грузополучателя.</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Срок поставки: сентябрь 2026 г.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>2431.2</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>6078</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>2431.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Досрочная поставка может производиться только с письменного согласия Заказчика.</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Продукция должна быть новой и ранее не использованной, и изготовлена в 2025-2026 гг.</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Трубы должны быть мерной длинны от 8 м до 12,5 м каждая.</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Поставляемая продукция по своему качеству должна соответствовать техническим требованиям, указанным в столбце №2 и соответствовать:
+- Техническому регламенту Таможенного союза «О безопасности оборудования работающего под избыточным давлением» ТР ТС 032/2013. 
+- Поставляемая продукция по своему качеству должна соответствовать техническим требованиям, указанным в столбце №2. 
+- Подтверждаться сертификатом качества завода-изготовителя.</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Поставляемая продукция должна подтверждаться сертификатом качества завода – изготовителя. Поставщик обязуется до момента отгрузки Продукции передать Покупателю заверенную заводом-изготовителем копию сертификата качества и соответствия, а также, по требованию Покупателя, предоставить гарантийное письмо от завода – изготовителя. Необходимые документы на продукцию (паспорт, сертификаты, товарно-транспортную накладную и т. д.) предоставляются не позднее момента фактического получения продукции.</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Гарантийный срок эксплуатации Продукции составляет не менее 24 месяцев с момента поставки Продукции Покупателю. Для труб, устанавливаемых на тепловых сетях - 10 лет с даты получения Покупателем Продукции. Полный назначенный срок службы - не менее 30 лет.</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Поставщик должен гарантировать безопасность продукции для жизни, здоровья, имущества Заказчика и окружающей среды при обычных условиях его использования, хранения, транспортировки и утилизации.</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Поставляемый товар должен быть экологически безопасен, сертифицирован и по безопасности должен соответствовать требованиям государственных стандартов, техническим условиям и действующему законодательству России.</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Реквизиты для счетов-фактур и Грузополучатель в соответствии со столбцом 10 Спецификации.</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>7.863378567499926e+16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="E16" s="6" t="n">
+        <v>93.288</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Источник: Проект договора (типовой) поставки ТРУБ (партии).docx</t>
         </is>
